--- a/output7/【河洛文讀注音-閩拼調號】《深慮論》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調號】《深慮論》.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91546C5A-C62C-4C72-BA55-A31C2CD58C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6D868B6-D1B5-4AC3-8ACB-D79C4FB9051D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="718" activeTab="6" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" tabRatio="718" activeTab="6" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
